--- a/docs/exports/club/03835845_Informatics_Institute_of_Technology.xlsx
+++ b/docs/exports/club/03835845_Informatics_Institute_of_Technology.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/club/03835845_Informatics_Institute_of_Technology.xlsx
+++ b/docs/exports/club/03835845_Informatics_Institute_of_Technology.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/club/03835845_Informatics_Institute_of_Technology.xlsx
+++ b/docs/exports/club/03835845_Informatics_Institute_of_Technology.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/club/03835845_Informatics_Institute_of_Technology.xlsx
+++ b/docs/exports/club/03835845_Informatics_Institute_of_Technology.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -634,25 +634,25 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>96</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Out of 158 active clubs district-wide.</t>
+          <t>Out of 157 active clubs district-wide.</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/club/03835845_Informatics_Institute_of_Technology.xlsx
+++ b/docs/exports/club/03835845_Informatics_Institute_of_Technology.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -547,13 +547,13 @@
         <v>1</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -634,25 +634,25 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>31</v>
+        <v>102</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>71</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Out of 157 active clubs district-wide.</t>
+          <t>Out of 155 active clubs district-wide.</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -728,13 +728,13 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B7" s="6" t="n">
         <v>4</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>

--- a/docs/exports/club/03835845_Informatics_Institute_of_Technology.xlsx
+++ b/docs/exports/club/03835845_Informatics_Institute_of_Technology.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/club/03835845_Informatics_Institute_of_Technology.xlsx
+++ b/docs/exports/club/03835845_Informatics_Institute_of_Technology.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-03-05  |  Report generated 02 Jul 2026, 20:33  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -547,13 +547,13 @@
         <v>1</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-03-05  |  Report generated 02 Jul 2026, 20:33  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -634,25 +634,25 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Out of 155 active clubs district-wide.</t>
+          <t>Out of 162 active clubs district-wide.</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-03-05  |  Report generated 02 Jul 2026, 20:33  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -728,13 +728,13 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
